--- a/artfynd/A 29371-2025 artfynd.xlsx
+++ b/artfynd/A 29371-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>4165638</v>
       </c>
       <c r="B2" t="n">
-        <v>95510</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,19 +690,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>286294.6553532733</v>
+        <v>286295</v>
       </c>
       <c r="R2" t="n">
-        <v>6508963.041275137</v>
+        <v>6508963</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +739,9 @@
           <t>1995-07-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1995-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
